--- a/data/trans_orig/IQ12A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de días que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores según el número de días que limitaron su actividad por dolores o síntomas (tasa de respuesta: 97,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,62</t>
+          <t>1,06; 3,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,64</t>
+          <t>2,81; 4,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 7,98</t>
+          <t>2,29; 8,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,85</t>
+          <t>2,53; 4,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,58</t>
+          <t>2,01; 6,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,83</t>
+          <t>1,79; 4,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,95</t>
+          <t>1,0; 3,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 6,81</t>
+          <t>3,77; 6,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,18</t>
+          <t>1,78; 4,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,03</t>
+          <t>2,6; 4,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,73</t>
+          <t>1,84; 5,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 5,59</t>
+          <t>3,39; 5,41</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,54</t>
+          <t>2,07; 3,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,84</t>
+          <t>2,25; 5,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,55</t>
+          <t>2,16; 4,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 5,72</t>
+          <t>3,58; 5,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 5,6</t>
+          <t>3,22; 5,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,78</t>
+          <t>2,61; 5,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,92</t>
+          <t>1,95; 4,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 8,03</t>
+          <t>4,34; 7,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 4,5</t>
+          <t>2,94; 4,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,64</t>
+          <t>2,66; 4,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,79</t>
+          <t>2,2; 3,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 6,75</t>
+          <t>4,39; 6,93</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,46</t>
+          <t>2,62; 5,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,48</t>
+          <t>2,66; 7,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,24</t>
+          <t>1,92; 3,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,49</t>
+          <t>2,62; 5,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,12</t>
+          <t>1,52; 5,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,45</t>
+          <t>2,82; 5,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,17</t>
+          <t>2,73; 5,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,43; 7,18</t>
+          <t>3,35; 7,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,59</t>
+          <t>2,51; 4,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 5,48</t>
+          <t>3,12; 5,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 3,97</t>
+          <t>2,49; 3,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,7</t>
+          <t>3,31; 5,68</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 11,42</t>
+          <t>4,9; 11,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,77</t>
+          <t>2,15; 3,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,77</t>
+          <t>2,85; 5,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 6,45</t>
+          <t>4,17; 6,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 7,6</t>
+          <t>3,36; 7,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,53</t>
+          <t>2,63; 5,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 7,52</t>
+          <t>2,85; 7,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 6,01</t>
+          <t>3,3; 5,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,17</t>
+          <t>4,58; 8,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,4</t>
+          <t>2,66; 4,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 5,59</t>
+          <t>3,16; 5,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,8</t>
+          <t>3,92; 5,79</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,75</t>
+          <t>2,96; 4,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,2</t>
+          <t>2,94; 4,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,25</t>
+          <t>2,65; 4,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,98</t>
+          <t>3,69; 4,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,05</t>
+          <t>3,18; 4,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 4,39</t>
+          <t>2,98; 4,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,82</t>
+          <t>2,58; 4,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,12</t>
+          <t>4,42; 6,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 4,49</t>
+          <t>3,26; 4,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,04</t>
+          <t>3,08; 4,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 3,76</t>
+          <t>2,76; 3,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,35</t>
+          <t>4,24; 5,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ12A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de días que limitaron su actividad por dolores o síntomas (tasa de respuesta: 97,76%)</t>
+          <t>Tiempo medio en días que limitaron su actividad en las últimas 2 semanas por dolores o síntomas (tasa de respuesta: 97,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,55</t>
+          <t>1,11; 4,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,62</t>
+          <t>2,7; 4,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,94</t>
+          <t>2,26; 8,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,9</t>
+          <t>2,59; 4,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 6,6</t>
+          <t>2,21; 6,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,0</t>
+          <t>1,81; 3,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,22</t>
+          <t>1,0; 3,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 6,58</t>
+          <t>3,67; 6,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,53</t>
+          <t>1,84; 4,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,08</t>
+          <t>2,55; 4,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,73</t>
+          <t>1,83; 5,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,41</t>
+          <t>3,43; 5,46</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,55</t>
+          <t>2,11; 3,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,13</t>
+          <t>2,23; 5,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,62</t>
+          <t>2,18; 4,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 5,78</t>
+          <t>3,65; 5,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,64</t>
+          <t>3,18; 5,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,46</t>
+          <t>2,65; 5,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,17</t>
+          <t>1,96; 3,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,84</t>
+          <t>4,25; 8,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,62</t>
+          <t>2,91; 4,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,6</t>
+          <t>2,67; 4,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,78</t>
+          <t>2,19; 3,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,93</t>
+          <t>4,39; 6,76</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,34</t>
+          <t>2,73; 5,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,31</t>
+          <t>2,55; 7,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,22</t>
+          <t>1,92; 3,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,8</t>
+          <t>2,62; 5,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,93</t>
+          <t>1,55; 6,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,67</t>
+          <t>2,78; 5,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,06</t>
+          <t>2,75; 5,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 7,43</t>
+          <t>3,39; 7,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,97</t>
+          <t>2,47; 4,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 5,43</t>
+          <t>3,16; 5,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,9</t>
+          <t>2,5; 3,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,68</t>
+          <t>3,29; 5,7</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,9; 11,15</t>
+          <t>4,63; 10,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,89</t>
+          <t>2,1; 3,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,79</t>
+          <t>2,89; 5,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,45</t>
+          <t>4,07; 6,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 7,32</t>
+          <t>3,4; 7,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,43</t>
+          <t>2,62; 5,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,0</t>
+          <t>2,9; 7,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,8</t>
+          <t>3,3; 5,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 8,05</t>
+          <t>4,59; 8,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,46</t>
+          <t>2,7; 4,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,64</t>
+          <t>3,13; 5,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 5,79</t>
+          <t>3,93; 5,66</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,68</t>
+          <t>2,83; 4,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,17</t>
+          <t>2,89; 4,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,23</t>
+          <t>2,67; 4,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,69; 4,95</t>
+          <t>3,67; 4,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,91</t>
+          <t>3,22; 4,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,42</t>
+          <t>2,97; 4,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,0</t>
+          <t>2,53; 3,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 6,1</t>
+          <t>4,36; 6,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,46</t>
+          <t>3,29; 4,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 4,07</t>
+          <t>3,12; 4,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,84</t>
+          <t>2,76; 3,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,38</t>
+          <t>4,24; 5,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ12A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Habitat-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,58</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,67</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,47</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5,51</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,88</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,59</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4,1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,51</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,58</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,67</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>3,46</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,43</t>
+          <t>4,44</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,01</t>
+          <t>2,12; 6,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,8</t>
+          <t>1,86; 3,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 8,05</t>
+          <t>1,0; 2,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,83</t>
+          <t>3,97; 6,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,88</t>
+          <t>1,05; 3,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,92</t>
+          <t>2,76; 4,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,02</t>
+          <t>2,16; 7,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 6,66</t>
+          <t>2,37; 4,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,28</t>
+          <t>1,8; 4,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 4,0</t>
+          <t>2,58; 4,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,78</t>
+          <t>1,87; 5,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,46</t>
+          <t>3,46; 5,61</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,18</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,7</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,62</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6,05</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,72</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,25</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>3,03</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,7</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,18</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,7</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,62</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,93</t>
+          <t>4,71</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,4</t>
+          <t>5,48</t>
         </is>
       </c>
     </row>
@@ -856,42 +856,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,6</t>
+          <t>3,2; 5,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,11</t>
+          <t>2,66; 5,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,65</t>
+          <t>1,92; 3,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 5,85</t>
+          <t>4,26; 8,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 5,67</t>
+          <t>2,05; 3,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,58</t>
+          <t>2,2; 4,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,99</t>
+          <t>2,1; 4,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,03</t>
+          <t>3,58; 5,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,71</t>
+          <t>2,7; 4,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,8</t>
+          <t>2,22; 3,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,76</t>
+          <t>4,45; 6,91</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,65</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,87</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,58</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5,09</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3,86</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,62</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,41</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,53</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,65</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,87</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,58</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,02</t>
+          <t>3,43</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,33</t>
+          <t>4,31</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,38</t>
+          <t>1,52; 6,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 7,1</t>
+          <t>2,84; 5,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,38</t>
+          <t>2,74; 5,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,61</t>
+          <t>3,5; 7,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,64</t>
+          <t>2,8; 5,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,55</t>
+          <t>2,7; 7,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,15</t>
+          <t>1,92; 3,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 7,28</t>
+          <t>2,49; 5,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,73</t>
+          <t>2,48; 4,59</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,33</t>
+          <t>3,15; 5,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 3,89</t>
+          <t>2,5; 3,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,7</t>
+          <t>3,32; 5,66</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,05</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,72</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,56</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7,76</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,89</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,79</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,05</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,72</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,4</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>4,85</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 10,96</t>
+          <t>3,49; 7,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,8</t>
+          <t>2,59; 5,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,9</t>
+          <t>2,94; 7,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,49</t>
+          <t>3,35; 6,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 7,45</t>
+          <t>4,75; 11,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,38</t>
+          <t>2,1; 3,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,38</t>
+          <t>2,86; 5,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,95</t>
+          <t>4,16; 6,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,49</t>
+          <t>4,42; 8,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,49</t>
+          <t>2,65; 4,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,49</t>
+          <t>3,04; 5,59</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,66</t>
+          <t>3,99; 5,84</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,59</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5,29</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>3,46</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3,26</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,25</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,95</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,59</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,13</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>4,2</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>4,8</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,75</t>
+          <t>3,22; 5,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,18</t>
+          <t>2,99; 4,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,15</t>
+          <t>2,54; 3,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 4,92</t>
+          <t>4,49; 6,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 4,91</t>
+          <t>2,94; 4,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 4,38</t>
+          <t>2,87; 4,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,89</t>
+          <t>2,65; 4,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,11</t>
+          <t>3,63; 4,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,58</t>
+          <t>3,23; 4,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,04</t>
+          <t>3,11; 4,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,83</t>
+          <t>2,77; 3,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,41</t>
+          <t>4,25; 5,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ12A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en días que limitaron su actividad en las últimas 2 semanas por dolores o síntomas (tasa de respuesta: 97,76%)</t>
+          <t>Tiempo medio en días que los menores limitaron su actividad en las últimas 2 semanas por dolores o síntomas (tasa de respuesta: 97,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,58</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,67</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,51</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,59</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3,46</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2,74</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3,25</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2,99</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,44</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.583753658686222</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.669282611106247</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.472530045021373</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>5.508045109957537</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1.880268113672807</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>3.590581466986638</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>4.102043924660603</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>3.459225241261968</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>2.738047101722409</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>3.24665086303907</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>2.993544564065278</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>4.440841407525617</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2,12; 6,58</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,86; 3,83</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 2,95</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3,97; 6,93</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,05; 3,62</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,76; 4,64</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2,16; 7,98</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2,37; 4,79</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1,8; 4,18</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2,58; 4,03</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1,87; 5,73</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,46; 5,61</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2.118370194607975</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1.857288160767565</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>3.969654072113797</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>1.053668351785225</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>2.764228361520872</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>2.15765204842854</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>2.373811069292608</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>1.803422024461798</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>2.576456764935105</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>1.87034162783502</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>3.456518862434</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.577518591389985</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.833803516443743</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.94517208516066</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6.927109553834344</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>3.618069767039441</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>4.640616046215979</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>7.980145359302442</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>4.789761340271276</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>4.180548947146199</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>4.030113642834809</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>5.726803915326859</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>5.61067571426103</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,18</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3,7</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,62</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,05</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,72</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,25</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,03</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4,71</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3,57</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3,45</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2,85</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,48</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>3,2; 5,6</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2,66; 5,78</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,92; 3,92</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4,26; 8,16</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,05; 3,54</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,2; 4,84</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,1; 4,55</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3,58; 5,77</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2,91; 4,5</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2,7; 4,64</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2,22; 3,79</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,45; 6,91</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>4.175222498915596</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3.699546866952083</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.615715046974809</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6.053393827228064</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>2.723428811089721</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>3.253279072485098</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>3.033158420671256</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>4.705828568424361</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>3.568215030121483</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>3.449861554888775</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>2.849637102627408</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>5.484348337928314</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,65</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,87</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,58</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,09</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,86</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,62</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,41</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3,43</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3,37</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>4,12</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3,07</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>4,31</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>3.197196623045325</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2.664806144740572</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1.915188521132685</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>4.264135916018122</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>2.05140249330201</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>2.203952520083433</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>2.100026303537713</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>3.576964339598335</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>2.908291588791289</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>2.702562192590062</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>2.223562571399213</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>4.451775468512391</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 6,12</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2,84; 5,45</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2,74; 5,17</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3,5; 7,16</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2,8; 5,46</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>2,7; 7,48</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,92; 3,24</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2,49; 5,25</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2,48; 4,59</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>3,15; 5,48</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2,5; 3,97</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>3,32; 5,66</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.596520297426927</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5.780107021445106</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.922289619480254</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>8.158693357180962</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>3.540286384977538</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>4.843680596608428</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>4.548589719067133</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>5.770622493472684</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>4.504067131897304</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>4.644648071509839</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>3.786749529521201</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>6.907252064572901</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>5,05</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3,72</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4,4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,56</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,76</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,89</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,79</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6,16</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3,36</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4,03</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,85</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>2.646923628459997</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.870044385825437</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3.578438996409627</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>5.086226411095863</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>3.859196779812757</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>4.624122918980538</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>2.407730556126979</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>3.434266652920741</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>3.365906660845157</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>4.115393427824157</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>3.071090382400334</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>4.308022442462685</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>3,49; 7,6</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2,59; 5,53</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2,94; 7,52</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3,35; 6,04</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4,75; 11,42</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2,1; 3,77</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2,86; 5,77</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4,16; 6,47</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4,42; 8,17</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2,65; 4,4</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3,04; 5,59</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>3,99; 5,84</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.524916354043897</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>2.842710159495058</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2.744380887492945</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>3.50158491254499</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>2.802404611498359</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>2.698011189503053</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>1.920378910034184</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>2.490241870200865</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>2.484056438276236</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>3.152982699505192</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>2.502465477541908</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>3.315994786506475</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6.119336001929821</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.446485811686858</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.173575257893271</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.162331823054534</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>5.463838105700452</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>7.4823880225094</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>3.240322869179317</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>5.248578786121002</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>4.585289582579202</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>5.482825211431148</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>3.966765371102895</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>5.658529393332784</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>5.04850964773722</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3.722497414222825</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>4.395350382091739</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>4.555096151336614</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>7.758435493696838</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>2.888411583185283</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>3.789867475746689</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>5.291721955242633</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>6.159882593322095</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>3.362051824499435</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>4.026669172005754</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>4.849960931089043</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>3.487522960829711</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>2.589833250059487</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>2.937241217020095</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>3.349802382431808</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>4.752081374346012</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>2.096324836888249</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>2.856391579801265</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>4.161189284450169</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>4.416089676347783</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>2.654107308784865</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>3.042161508169965</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>3.994351355839256</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.597223519001275</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.529455577244928</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.522543720905077</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.037919277796071</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>11.41706283335067</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>3.768525252875385</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>5.770640895798553</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>6.467050519305798</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>8.172989997636037</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>4.403154986447682</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>5.594129606944224</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>5.841436428300685</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,95</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3,59</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,13</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,66</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,46</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,26</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4,2</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3,81</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3,52</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,8</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>3,22; 5,05</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2,99; 4,39</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2,54; 3,82</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4,49; 6,23</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,94; 4,75</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,87; 4,2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,65; 4,25</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3,63; 4,9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3,23; 4,49</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3,11; 4,04</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2,77; 3,76</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,25; 5,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>3.945601916730845</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3.588834497697063</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>3.133645839672639</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>5.2883898255871</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>3.656725791927583</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>3.456844234535392</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>3.264182514215749</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>4.196507506838844</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>3.807920160023901</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>3.524737585550751</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>3.20405118490479</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>4.799125101621544</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>3.216835100523757</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>2.98630270680005</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>2.537059761609317</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>4.491646449014863</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>2.93737531074011</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>2.872547917331249</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>2.654237545863394</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>3.630459632788607</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>3.232162117499079</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>3.106832931488398</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>2.766593329066177</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>4.251364057267459</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.051663667690388</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>4.394134864994804</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.816646597527908</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>6.234195483667308</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>4.747348062115237</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>4.197378411003905</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>4.248348263941926</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>4.903035894506758</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>4.487814821461741</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>4.039193618632256</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>3.75975515804398</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>5.378420792859535</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
